--- a/resources/ShotTracker-ScoreCalculator(spreadsheet).xlsx
+++ b/resources/ShotTracker-ScoreCalculator(spreadsheet).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin64\home\donha\cs320-spring2024\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E27F96C-DD15-4267-B106-8BCF2E9A20E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D4BFE9B-1EA0-46B0-8152-D229E358623B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5940" yWindow="585" windowWidth="23333" windowHeight="15127" activeTab="1" xr2:uid="{A1A8451F-B533-4806-BB6B-F3885EFA9270}"/>
+    <workbookView xWindow="5468" yWindow="473" windowWidth="23332" windowHeight="15127" activeTab="1" xr2:uid="{A1A8451F-B533-4806-BB6B-F3885EFA9270}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/resources/ShotTracker-ScoreCalculator(spreadsheet).xlsx
+++ b/resources/ShotTracker-ScoreCalculator(spreadsheet).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin64\home\donha\cs320-spring2024\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E97D0B70-13C7-4A69-964E-4A9B5889A7DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE61F83D-9AAE-4EEE-9AF1-09C0FF09F5C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1357" yWindow="285" windowWidth="26813" windowHeight="15128" activeTab="2" xr2:uid="{A1A8451F-B533-4806-BB6B-F3885EFA9270}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="83">
   <si>
     <t>count</t>
   </si>
@@ -284,6 +284,9 @@
   </si>
   <si>
     <t>LEAVE</t>
+  </si>
+  <si>
+    <t>BL</t>
   </si>
 </sst>
 </file>
@@ -1098,8 +1101,9 @@
   <dimension ref="A1:R522"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.9296875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="13" width="9.06640625" style="13"/>
+    <col min="1" max="2" width="9.06640625" style="13"/>
+    <col min="3" max="3" width="9.9296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="13" width="9.06640625" style="13"/>
     <col min="14" max="14" width="9.06640625" style="10"/>
     <col min="15" max="15" width="9.06640625" style="13"/>
     <col min="16" max="16" width="9.06640625" style="10"/>
@@ -1107,23 +1111,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="5" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="D1" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="E1" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="F1" s="12" t="s">
         <v>80</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>28</v>
       </c>
       <c r="G1" s="12" t="s">
         <v>27</v>
@@ -1163,20 +1167,22 @@
       </c>
     </row>
     <row r="2" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="20">
+      <c r="A2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="17"/>
+      <c r="C2" s="20">
         <v>33855</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>75</v>
       </c>
       <c r="D2" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
+      <c r="E2" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>20</v>
+      </c>
       <c r="G2" s="17"/>
       <c r="H2" s="17">
         <v>1</v>
@@ -1455,9 +1461,9 @@
       </c>
     </row>
     <row r="16" spans="1:18" s="16" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="21"/>
+      <c r="A16" s="14"/>
       <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
+      <c r="C16" s="21"/>
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
       <c r="F16" s="14"/>
@@ -1822,9 +1828,9 @@
       </c>
     </row>
     <row r="35" spans="1:17" s="16" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="21"/>
+      <c r="A35" s="14"/>
       <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
+      <c r="C35" s="21"/>
       <c r="D35" s="14"/>
       <c r="E35" s="14"/>
       <c r="F35" s="14"/>
@@ -2101,20 +2107,22 @@
       </c>
     </row>
     <row r="49" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A49" s="20">
+      <c r="A49" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="B49" s="17"/>
+      <c r="C49" s="20">
         <v>33862</v>
       </c>
-      <c r="B49" s="17">
-        <v>1</v>
-      </c>
-      <c r="C49" s="17">
-        <v>2</v>
-      </c>
       <c r="D49" s="17">
-        <v>2</v>
-      </c>
-      <c r="E49" s="17"/>
-      <c r="F49" s="17"/>
+        <v>1</v>
+      </c>
+      <c r="E49" s="17">
+        <v>2</v>
+      </c>
+      <c r="F49" s="17">
+        <v>2</v>
+      </c>
       <c r="G49" s="17"/>
       <c r="H49" s="17">
         <v>1</v>
@@ -2427,9 +2435,9 @@
       </c>
     </row>
     <row r="65" spans="1:17" s="16" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A65" s="21"/>
+      <c r="A65" s="14"/>
       <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
+      <c r="C65" s="21"/>
       <c r="D65" s="14"/>
       <c r="E65" s="14"/>
       <c r="F65" s="14"/>
@@ -2714,9 +2722,9 @@
       </c>
     </row>
     <row r="79" spans="1:17" s="16" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A79" s="21"/>
+      <c r="A79" s="14"/>
       <c r="B79" s="14"/>
-      <c r="C79" s="14"/>
+      <c r="C79" s="21"/>
       <c r="D79" s="14"/>
       <c r="E79" s="14"/>
       <c r="F79" s="14"/>
@@ -3018,20 +3026,22 @@
       </c>
     </row>
     <row r="94" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A94" s="20">
+      <c r="A94" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="B94" s="17"/>
+      <c r="C94" s="20">
         <v>33869</v>
-      </c>
-      <c r="B94" s="17">
-        <v>3</v>
-      </c>
-      <c r="C94" s="17">
-        <v>4</v>
       </c>
       <c r="D94" s="17">
         <v>3</v>
       </c>
-      <c r="E94" s="17"/>
-      <c r="F94" s="17"/>
+      <c r="E94" s="17">
+        <v>4</v>
+      </c>
+      <c r="F94" s="17">
+        <v>3</v>
+      </c>
       <c r="G94" s="17"/>
       <c r="H94" s="17">
         <v>1</v>
@@ -3367,9 +3377,9 @@
       </c>
     </row>
     <row r="111" spans="1:17" s="16" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A111" s="21"/>
+      <c r="A111" s="14"/>
       <c r="B111" s="14"/>
-      <c r="C111" s="14"/>
+      <c r="C111" s="21"/>
       <c r="D111" s="14"/>
       <c r="E111" s="14"/>
       <c r="F111" s="14"/>
@@ -3697,9 +3707,9 @@
       </c>
     </row>
     <row r="128" spans="1:17" s="16" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A128" s="21"/>
+      <c r="A128" s="14"/>
       <c r="B128" s="14"/>
-      <c r="C128" s="14"/>
+      <c r="C128" s="21"/>
       <c r="D128" s="14"/>
       <c r="E128" s="14"/>
       <c r="F128" s="14"/>
@@ -3998,20 +4008,22 @@
       </c>
     </row>
     <row r="143" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A143" s="20">
+      <c r="A143" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="B143" s="17"/>
+      <c r="C143" s="20">
         <v>33876</v>
       </c>
-      <c r="B143" s="17">
+      <c r="D143" s="17">
         <v>13</v>
       </c>
-      <c r="C143" s="17">
+      <c r="E143" s="17">
         <v>14</v>
       </c>
-      <c r="D143" s="17">
+      <c r="F143" s="17">
         <v>14</v>
       </c>
-      <c r="E143" s="17"/>
-      <c r="F143" s="17"/>
       <c r="G143" s="17"/>
       <c r="H143" s="17">
         <v>1</v>
@@ -4287,9 +4299,9 @@
       </c>
     </row>
     <row r="157" spans="1:17" s="16" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A157" s="21"/>
+      <c r="A157" s="14"/>
       <c r="B157" s="14"/>
-      <c r="C157" s="14"/>
+      <c r="C157" s="21"/>
       <c r="D157" s="14"/>
       <c r="E157" s="14"/>
       <c r="F157" s="14"/>
@@ -4606,9 +4618,9 @@
       </c>
     </row>
     <row r="173" spans="1:17" s="16" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A173" s="21"/>
+      <c r="A173" s="14"/>
       <c r="B173" s="14"/>
-      <c r="C173" s="14"/>
+      <c r="C173" s="21"/>
       <c r="D173" s="14"/>
       <c r="E173" s="14"/>
       <c r="F173" s="14"/>
@@ -4904,20 +4916,22 @@
       </c>
     </row>
     <row r="188" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A188" s="20">
+      <c r="A188" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="B188" s="17"/>
+      <c r="C188" s="20">
         <v>33883</v>
-      </c>
-      <c r="B188" s="17">
-        <v>19</v>
-      </c>
-      <c r="C188" s="17">
-        <v>20</v>
       </c>
       <c r="D188" s="17">
         <v>19</v>
       </c>
-      <c r="E188" s="17"/>
-      <c r="F188" s="17"/>
+      <c r="E188" s="17">
+        <v>20</v>
+      </c>
+      <c r="F188" s="17">
+        <v>19</v>
+      </c>
       <c r="G188" s="17"/>
       <c r="H188" s="17">
         <v>1</v>
@@ -5250,9 +5264,9 @@
       </c>
     </row>
     <row r="205" spans="1:17" s="16" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A205" s="21"/>
+      <c r="A205" s="14"/>
       <c r="B205" s="14"/>
-      <c r="C205" s="14"/>
+      <c r="C205" s="21"/>
       <c r="D205" s="14"/>
       <c r="E205" s="14"/>
       <c r="F205" s="14"/>
@@ -5582,9 +5596,9 @@
       </c>
     </row>
     <row r="222" spans="1:17" s="16" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A222" s="21"/>
+      <c r="A222" s="14"/>
       <c r="B222" s="14"/>
-      <c r="C222" s="14"/>
+      <c r="C222" s="21"/>
       <c r="D222" s="14"/>
       <c r="E222" s="14"/>
       <c r="F222" s="14"/>
@@ -5900,20 +5914,22 @@
       </c>
     </row>
     <row r="238" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A238" s="20">
+      <c r="A238" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="B238" s="17"/>
+      <c r="C238" s="20">
         <v>33890</v>
       </c>
-      <c r="B238" s="17">
-        <v>9</v>
-      </c>
-      <c r="C238" s="17">
-        <v>10</v>
-      </c>
       <c r="D238" s="17">
-        <v>10</v>
-      </c>
-      <c r="E238" s="17"/>
-      <c r="F238" s="17"/>
+        <v>9</v>
+      </c>
+      <c r="E238" s="17">
+        <v>10</v>
+      </c>
+      <c r="F238" s="17">
+        <v>10</v>
+      </c>
       <c r="G238" s="17"/>
       <c r="H238" s="17">
         <v>1</v>
@@ -6282,9 +6298,9 @@
       </c>
     </row>
     <row r="257" spans="1:17" s="16" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A257" s="21"/>
+      <c r="A257" s="14"/>
       <c r="B257" s="14"/>
-      <c r="C257" s="14"/>
+      <c r="C257" s="21"/>
       <c r="D257" s="14"/>
       <c r="E257" s="14"/>
       <c r="F257" s="14"/>
@@ -6603,9 +6619,9 @@
       </c>
     </row>
     <row r="273" spans="1:17" s="16" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A273" s="21"/>
+      <c r="A273" s="14"/>
       <c r="B273" s="14"/>
-      <c r="C273" s="14"/>
+      <c r="C273" s="21"/>
       <c r="D273" s="14"/>
       <c r="E273" s="14"/>
       <c r="F273" s="14"/>
@@ -6952,20 +6968,22 @@
       </c>
     </row>
     <row r="291" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A291" s="20">
+      <c r="A291" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="B291" s="17"/>
+      <c r="C291" s="20">
         <v>33897</v>
-      </c>
-      <c r="B291" s="17">
-        <v>5</v>
-      </c>
-      <c r="C291" s="17">
-        <v>6</v>
       </c>
       <c r="D291" s="17">
         <v>5</v>
       </c>
-      <c r="E291" s="17"/>
-      <c r="F291" s="17"/>
+      <c r="E291" s="17">
+        <v>6</v>
+      </c>
+      <c r="F291" s="17">
+        <v>5</v>
+      </c>
       <c r="G291" s="17"/>
       <c r="H291" s="17">
         <v>1</v>
@@ -7258,9 +7276,9 @@
       </c>
     </row>
     <row r="306" spans="1:17" s="16" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A306" s="22"/>
+      <c r="A306" s="14"/>
       <c r="B306" s="14"/>
-      <c r="C306" s="14"/>
+      <c r="C306" s="22"/>
       <c r="D306" s="14"/>
       <c r="E306" s="14"/>
       <c r="F306" s="14"/>
@@ -7539,9 +7557,9 @@
       </c>
     </row>
     <row r="320" spans="1:17" s="16" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A320" s="21"/>
+      <c r="A320" s="14"/>
       <c r="B320" s="14"/>
-      <c r="C320" s="14"/>
+      <c r="C320" s="21"/>
       <c r="D320" s="14"/>
       <c r="E320" s="14"/>
       <c r="F320" s="14"/>
@@ -7857,20 +7875,22 @@
       </c>
     </row>
     <row r="336" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A336" s="20">
+      <c r="A336" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="B336" s="17"/>
+      <c r="C336" s="20">
         <v>33904</v>
-      </c>
-      <c r="B336" s="17">
-        <v>17</v>
-      </c>
-      <c r="C336" s="17">
-        <v>18</v>
       </c>
       <c r="D336" s="17">
         <v>17</v>
       </c>
-      <c r="E336" s="17"/>
-      <c r="F336" s="17"/>
+      <c r="E336" s="17">
+        <v>18</v>
+      </c>
+      <c r="F336" s="17">
+        <v>17</v>
+      </c>
       <c r="G336" s="17"/>
       <c r="H336" s="17">
         <v>1</v>
@@ -8148,9 +8168,9 @@
       </c>
     </row>
     <row r="350" spans="1:17" s="16" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A350" s="21"/>
+      <c r="A350" s="14"/>
       <c r="B350" s="14"/>
-      <c r="C350" s="14"/>
+      <c r="C350" s="21"/>
       <c r="D350" s="14"/>
       <c r="E350" s="14"/>
       <c r="F350" s="14"/>
@@ -8446,9 +8466,9 @@
       </c>
     </row>
     <row r="365" spans="1:17" s="16" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A365" s="21"/>
+      <c r="A365" s="14"/>
       <c r="B365" s="14"/>
-      <c r="C365" s="14"/>
+      <c r="C365" s="21"/>
       <c r="D365" s="14"/>
       <c r="E365" s="14"/>
       <c r="F365" s="14"/>
@@ -8781,20 +8801,22 @@
       </c>
     </row>
     <row r="382" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A382" s="20">
+      <c r="A382" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="B382" s="17"/>
+      <c r="C382" s="20">
         <v>33911</v>
       </c>
-      <c r="B382" s="17">
-        <v>7</v>
-      </c>
-      <c r="C382" s="17">
+      <c r="D382" s="17">
+        <v>7</v>
+      </c>
+      <c r="E382" s="17">
         <v>8</v>
       </c>
-      <c r="D382" s="17">
+      <c r="F382" s="17">
         <v>8</v>
       </c>
-      <c r="E382" s="17"/>
-      <c r="F382" s="17"/>
       <c r="G382" s="17"/>
       <c r="H382" s="17">
         <v>1</v>
@@ -9070,9 +9092,9 @@
       </c>
     </row>
     <row r="396" spans="1:17" s="16" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A396" s="21"/>
+      <c r="A396" s="14"/>
       <c r="B396" s="14"/>
-      <c r="C396" s="14"/>
+      <c r="C396" s="21"/>
       <c r="D396" s="14"/>
       <c r="E396" s="14"/>
       <c r="F396" s="14"/>
@@ -9351,9 +9373,9 @@
       </c>
     </row>
     <row r="410" spans="1:17" s="16" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A410" s="21"/>
+      <c r="A410" s="14"/>
       <c r="B410" s="14"/>
-      <c r="C410" s="14"/>
+      <c r="C410" s="21"/>
       <c r="D410" s="14"/>
       <c r="E410" s="14"/>
       <c r="F410" s="14"/>
@@ -9669,20 +9691,22 @@
       </c>
     </row>
     <row r="426" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A426" s="20">
+      <c r="A426" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="B426" s="17"/>
+      <c r="C426" s="20">
         <v>33918</v>
-      </c>
-      <c r="B426" s="17">
-        <v>11</v>
-      </c>
-      <c r="C426" s="17">
-        <v>12</v>
       </c>
       <c r="D426" s="17">
         <v>11</v>
       </c>
-      <c r="E426" s="17"/>
-      <c r="F426" s="17"/>
+      <c r="E426" s="17">
+        <v>12</v>
+      </c>
+      <c r="F426" s="17">
+        <v>11</v>
+      </c>
       <c r="G426" s="17"/>
       <c r="H426" s="17">
         <v>1</v>
@@ -10029,9 +10053,9 @@
       </c>
     </row>
     <row r="444" spans="1:17" s="16" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A444" s="21"/>
+      <c r="A444" s="14"/>
       <c r="B444" s="14"/>
-      <c r="C444" s="14"/>
+      <c r="C444" s="21"/>
       <c r="D444" s="14"/>
       <c r="E444" s="14"/>
       <c r="F444" s="14"/>
@@ -10361,9 +10385,9 @@
       </c>
     </row>
     <row r="461" spans="1:17" s="16" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A461" s="21"/>
+      <c r="A461" s="14"/>
       <c r="B461" s="14"/>
-      <c r="C461" s="14"/>
+      <c r="C461" s="21"/>
       <c r="D461" s="14"/>
       <c r="E461" s="14"/>
       <c r="F461" s="14"/>
@@ -10702,20 +10726,22 @@
       </c>
     </row>
     <row r="478" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A478" s="20">
+      <c r="A478" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="B478" s="17"/>
+      <c r="C478" s="20">
         <v>33925</v>
       </c>
-      <c r="B478" s="17">
+      <c r="D478" s="17">
         <v>11</v>
       </c>
-      <c r="C478" s="17">
+      <c r="E478" s="17">
         <v>12</v>
       </c>
-      <c r="D478" s="17">
+      <c r="F478" s="17">
         <v>12</v>
       </c>
-      <c r="E478" s="17"/>
-      <c r="F478" s="17"/>
       <c r="G478" s="17"/>
       <c r="H478" s="17">
         <v>1</v>
@@ -11062,9 +11088,9 @@
       </c>
     </row>
     <row r="496" spans="1:17" s="16" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A496" s="21"/>
+      <c r="A496" s="14"/>
       <c r="B496" s="14"/>
-      <c r="C496" s="14"/>
+      <c r="C496" s="21"/>
       <c r="D496" s="14"/>
       <c r="E496" s="14"/>
       <c r="F496" s="14"/>
@@ -11346,9 +11372,9 @@
       </c>
     </row>
     <row r="510" spans="1:17" s="16" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A510" s="21"/>
+      <c r="A510" s="14"/>
       <c r="B510" s="14"/>
-      <c r="C510" s="14"/>
+      <c r="C510" s="21"/>
       <c r="D510" s="14"/>
       <c r="E510" s="14"/>
       <c r="F510" s="14"/>

--- a/resources/ShotTracker-ScoreCalculator(spreadsheet).xlsx
+++ b/resources/ShotTracker-ScoreCalculator(spreadsheet).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin64\home\donha\cs320-spring2024\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE949C0A-FE9B-477E-8613-4624B9AA8D0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F085F0B8-6F58-453C-8371-1FD721C54AE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1357" yWindow="285" windowWidth="26813" windowHeight="15128" activeTab="2" xr2:uid="{A1A8451F-B533-4806-BB6B-F3885EFA9270}"/>
   </bookViews>
